--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81804\Desktop\quiz-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AD776D-9D7E-4261-ACAC-093B6B23895E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9410A8E8-E8C4-4FBF-BB38-2400BEF02288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
   </bookViews>
   <sheets>
     <sheet name="QuizData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
   <si>
     <t>答え</t>
     <rPh sb="0" eb="1">
@@ -502,6 +502,417 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>イショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛しき記憶の「返還者」 メモリー</t>
+    <rPh sb="0" eb="1">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キオク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>闇属性</t>
+    <rPh sb="0" eb="3">
+      <t>ヤミゾクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロボット族の貫通タイプ</t>
+    <rPh sb="4" eb="5">
+      <t>ゾク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肩からカメラを提げた姿</t>
+    <rPh sb="0" eb="1">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地雷に対応</t>
+    <rPh sb="0" eb="2">
+      <t>ジライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バランス型</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誕生日は３月１９日</t>
+    <rPh sb="0" eb="3">
+      <t>タンジョウビ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>好きなものはエーデルワイス</t>
+    <rPh sb="0" eb="1">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白い帽子を被った姿</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ボウシ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「レース」(爆絶)で大活躍しているキャラクターです</t>
+    <rPh sb="6" eb="8">
+      <t>バクゼツ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ダイカツヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暁闇なる天下五剣・真打 数珠丸恒次</t>
+    <rPh sb="0" eb="1">
+      <t>アカツキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シンウチ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジュズマル</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒサシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗い色の髪</t>
+    <rPh sb="0" eb="1">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒色を基調とした和装</t>
+    <rPh sb="0" eb="2">
+      <t>クロイロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キチョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ワソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫色の縁取りがある黒いフード</t>
+    <rPh sb="0" eb="2">
+      <t>ムラサキイロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フチド</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>好物のおはぎ</t>
+    <rPh sb="0" eb="2">
+      <t>コウブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>７月７日の誕生日</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>タンジョウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亡き親の面影を持つ神霊の使役</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オヤ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オモカゲ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シンレイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背後にそびえる青い炎の像</t>
+    <rPh sb="0" eb="2">
+      <t>ハイゴ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ロンギヌス」(超究極)でそこそこ使われているキャラクターです</t>
+    <rPh sb="8" eb="9">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キュウキョク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サムライ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剛勇なる噴炎の女戦士 スキッティ</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウユウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妖精族でダメージウォール対応</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウセイゾク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>反射タイプ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知能戦よりも肉弾戦を好む性格</t>
+    <rPh sb="0" eb="2">
+      <t>チノウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニクダンセン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コノ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肩に担いだ巨大な武器</t>
+    <rPh sb="0" eb="1">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「恭順の邪鉱神 ダマスカス廻」(超絶・廻)でそこそこ使われています</t>
+    <rPh sb="1" eb="3">
+      <t>キョウジュン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨコシマ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョウゼツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストライクショット名「ボルケーノ・ストロングボンド」</t>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎のたてがみを備えた青黒い獣が並び立つ姿</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ソナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>アオグロ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケモノ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火属性でウィンド対応</t>
+    <rPh sb="0" eb="3">
+      <t>ヒゾクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相棒の巨大な獣の名前はワイルディ</t>
+    <rPh sb="0" eb="2">
+      <t>アイボウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョダイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ケモノ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナマエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -887,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0233801E-AEE7-419F-A025-B14A53D8E071}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="36.58203125" customWidth="1"/>
@@ -1236,6 +1647,336 @@
         <v>38</v>
       </c>
     </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1243,15 +1984,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101003A98CDF2E9D52540902CCB3A4A89A347" ma:contentTypeVersion="5" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="edf6a6dfb2d0c2adb6df272bc5317342">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ff08aa26-24a3-496c-aaff-d3be2242e1de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9d4b6645e0fb865332f6bdb4b29f432" ns3:_="">
     <xsd:import namespace="ff08aa26-24a3-496c-aaff-d3be2242e1de"/>
@@ -1401,6 +2133,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1408,14 +2149,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6104DA49-E359-44CA-A396-FC261DBFC7A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1429,6 +2162,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81804\Desktop\quiz-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9410A8E8-E8C4-4FBF-BB38-2400BEF02288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C38B6F-E6C4-4F2E-AD99-A1DB7C71E446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
   </bookViews>
   <sheets>
     <sheet name="QuizData" sheetId="1" r:id="rId1"/>
@@ -195,32 +195,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>招福ガールズバンド えび天娘。</t>
-    <rPh sb="0" eb="1">
-      <t>マネ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ムスメ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>誓約の「錬金術師」 ファウスト</t>
-    <rPh sb="0" eb="2">
-      <t>セイヤク</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>レンキンジュツシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>種族は聖騎士</t>
     <rPh sb="0" eb="2">
       <t>シュゾク</t>
@@ -360,19 +334,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>眩きランプの聖天使 ナイチンゲール</t>
-    <rPh sb="0" eb="1">
-      <t>マブ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>テンシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>重力バリアと水属性キラー持ち</t>
     <rPh sb="0" eb="2">
       <t>ジュウリョク</t>
@@ -506,22 +467,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>愛しき記憶の「返還者」 メモリー</t>
-    <rPh sb="0" eb="1">
-      <t>イト</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キオク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>シャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>闇属性</t>
     <rPh sb="0" eb="3">
       <t>ヤミゾクセイ</t>
@@ -615,37 +560,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>暁闇なる天下五剣・真打 数珠丸恒次</t>
-    <rPh sb="0" eb="1">
-      <t>アカツキ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ヤミ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テンカ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シンウチ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ジュズマル</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヒサシ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>暗い色の髪</t>
     <rPh sb="0" eb="1">
       <t>クラ</t>
@@ -760,25 +674,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>剛勇なる噴炎の女戦士 スキッティ</t>
-    <rPh sb="0" eb="2">
-      <t>ゴウユウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>フン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ホノオ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>オンナ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>妖精族でダメージウォール対応</t>
     <rPh sb="0" eb="3">
       <t>ヨウセイゾク</t>
@@ -913,6 +808,117 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>招福ガールズバンド
+えび天娘。</t>
+    <rPh sb="0" eb="1">
+      <t>マネ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ムスメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誓約の「錬金術師」
+ファウスト</t>
+    <rPh sb="0" eb="2">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>レンキンジュツシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>眩きランプの聖天使
+ナイチンゲール</t>
+    <rPh sb="0" eb="1">
+      <t>マブ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛しき記憶の「返還者」
+メモリー</t>
+    <rPh sb="0" eb="1">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キオク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暁闇なる天下五剣・真打
+数珠丸恒次</t>
+    <rPh sb="0" eb="1">
+      <t>アカツキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤミ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シンウチ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジュズマル</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒサシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剛勇なる噴炎の女戦士
+スキッティ</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウユウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -960,9 +966,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,9 +1326,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="2" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1328,9 +1337,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>16</v>
+    <row r="3" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -1339,9 +1348,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>16</v>
+    <row r="4" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -1350,9 +1359,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>16</v>
+    <row r="5" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -1361,9 +1370,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>16</v>
+    <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -1372,9 +1381,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>16</v>
+    <row r="7" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -1383,9 +1392,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>16</v>
+    <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -1394,9 +1403,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>16</v>
+    <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -1405,9 +1414,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>16</v>
+    <row r="10" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -1416,9 +1425,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>16</v>
+    <row r="11" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -1427,471 +1436,471 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>17</v>
+    </row>
+    <row r="14" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>17</v>
+    <row r="21" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="25" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B34" t="s">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
         <v>39</v>
       </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>39</v>
+    </row>
+    <row r="37" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B47" t="s">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>49</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B54" t="s">
         <v>5</v>
@@ -1900,81 +1909,81 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>59</v>
+    <row r="55" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
         <v>59</v>
       </c>
-      <c r="B57" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>59</v>
+    </row>
+    <row r="59" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1984,6 +1993,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101003A98CDF2E9D52540902CCB3A4A89A347" ma:contentTypeVersion="5" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="edf6a6dfb2d0c2adb6df272bc5317342">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ff08aa26-24a3-496c-aaff-d3be2242e1de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9d4b6645e0fb865332f6bdb4b29f432" ns3:_="">
     <xsd:import namespace="ff08aa26-24a3-496c-aaff-d3be2242e1de"/>
@@ -2133,15 +2151,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2149,6 +2158,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6104DA49-E359-44CA-A396-FC261DBFC7A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2162,14 +2179,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81804\Desktop\quiz-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C38B6F-E6C4-4F2E-AD99-A1DB7C71E446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91C153C-B342-400D-87F6-CF192C8A869A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
   </bookViews>
@@ -812,8 +812,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>招福ガールズバンド
-えび天娘。</t>
+    <t>招福ガールズバンド えび天娘。</t>
     <rPh sb="0" eb="1">
       <t>マネ</t>
     </rPh>
@@ -821,16 +820,12 @@
       <t>フク</t>
     </rPh>
     <rPh sb="12" eb="13">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
       <t>ムスメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>誓約の「錬金術師」
-ファウスト</t>
+    <t>誓約の「錬金術師」 ファウスト</t>
     <rPh sb="0" eb="2">
       <t>セイヤク</t>
     </rPh>
@@ -840,8 +835,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>眩きランプの聖天使
-ナイチンゲール</t>
+    <t>眩きランプの聖天使 ナイチンゲール</t>
     <rPh sb="0" eb="1">
       <t>マブ</t>
     </rPh>
@@ -854,8 +848,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>愛しき記憶の「返還者」
-メモリー</t>
+    <t>愛しき記憶の「返還者」 メモリー</t>
     <rPh sb="0" eb="1">
       <t>イト</t>
     </rPh>
@@ -871,8 +864,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>暁闇なる天下五剣・真打
-数珠丸恒次</t>
+    <t>暁闇なる天下五剣・真打 数珠丸恒次</t>
     <rPh sb="0" eb="1">
       <t>アカツキ</t>
     </rPh>
@@ -903,8 +895,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>剛勇なる噴炎の女戦士
-スキッティ</t>
+    <t>剛勇なる噴炎の女戦士 スキッティ</t>
     <rPh sb="0" eb="2">
       <t>ゴウユウ</t>
     </rPh>
@@ -1326,7 +1317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>63</v>
       </c>
@@ -1337,7 +1328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>63</v>
       </c>
@@ -1348,7 +1339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>63</v>
       </c>
@@ -1359,7 +1350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>63</v>
       </c>
@@ -1370,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -1381,7 +1372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1392,7 +1383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
@@ -1403,7 +1394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>63</v>
       </c>
@@ -1414,7 +1405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>63</v>
       </c>
@@ -1425,7 +1416,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
@@ -1436,7 +1427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>64</v>
       </c>
@@ -1447,7 +1438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
@@ -1458,7 +1449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -1469,7 +1460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
@@ -1480,7 +1471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>64</v>
       </c>
@@ -1491,7 +1482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>64</v>
       </c>
@@ -1502,7 +1493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>64</v>
       </c>
@@ -1513,7 +1504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -1524,7 +1515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
@@ -1535,7 +1526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>64</v>
       </c>
@@ -1546,7 +1537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>65</v>
       </c>
@@ -1557,7 +1548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>65</v>
       </c>
@@ -1568,7 +1559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>65</v>
       </c>
@@ -1579,7 +1570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>65</v>
       </c>
@@ -1590,7 +1581,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1601,7 +1592,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -1612,7 +1603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -1623,7 +1614,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
@@ -1634,7 +1625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
@@ -1645,7 +1636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
@@ -1656,7 +1647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -1667,7 +1658,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
@@ -1678,7 +1669,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -1689,7 +1680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>66</v>
       </c>
@@ -1700,7 +1691,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>66</v>
       </c>
@@ -1711,7 +1702,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
@@ -1722,7 +1713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>66</v>
       </c>
@@ -1733,7 +1724,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>66</v>
       </c>
@@ -1744,7 +1735,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>66</v>
       </c>
@@ -1755,7 +1746,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>66</v>
       </c>
@@ -1766,7 +1757,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>67</v>
       </c>
@@ -1777,7 +1768,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>67</v>
       </c>
@@ -1788,7 +1779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>67</v>
       </c>
@@ -1799,7 +1790,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>67</v>
       </c>
@@ -1810,7 +1801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>67</v>
       </c>
@@ -1821,7 +1812,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>67</v>
       </c>
@@ -1832,7 +1823,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>67</v>
       </c>
@@ -1843,7 +1834,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>67</v>
       </c>
@@ -1854,7 +1845,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>67</v>
       </c>
@@ -1865,7 +1856,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>67</v>
       </c>
@@ -1876,7 +1867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
@@ -1887,7 +1878,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>68</v>
       </c>
@@ -1898,7 +1889,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>68</v>
       </c>
@@ -1909,7 +1900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -1920,7 +1911,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>68</v>
       </c>
@@ -1931,7 +1922,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>68</v>
       </c>
@@ -1942,7 +1933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>68</v>
       </c>
@@ -1953,7 +1944,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>68</v>
       </c>
@@ -1964,7 +1955,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -1975,7 +1966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>68</v>
       </c>
@@ -1993,15 +1984,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101003A98CDF2E9D52540902CCB3A4A89A347" ma:contentTypeVersion="5" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="edf6a6dfb2d0c2adb6df272bc5317342">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ff08aa26-24a3-496c-aaff-d3be2242e1de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9d4b6645e0fb865332f6bdb4b29f432" ns3:_="">
     <xsd:import namespace="ff08aa26-24a3-496c-aaff-d3be2242e1de"/>
@@ -2151,6 +2133,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2158,14 +2149,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6104DA49-E359-44CA-A396-FC261DBFC7A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2179,6 +2162,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/quizzes.xlsx
+++ b/data/quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81804\Desktop\quiz-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91C153C-B342-400D-87F6-CF192C8A869A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7536CE85-ABA6-42F0-817D-DDF5A7A92BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
+    <workbookView xWindow="10730" yWindow="0" windowWidth="8560" windowHeight="10170" xr2:uid="{E219D89E-BFCE-4023-B284-DDC4A2257DB3}"/>
   </bookViews>
   <sheets>
     <sheet name="QuizData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="89">
   <si>
     <t>答え</t>
     <rPh sb="0" eb="1">
@@ -910,6 +910,305 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>センシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>巨獣王に仕えし卜占官 スピリタス</t>
+    <rPh sb="0" eb="2">
+      <t>キョジュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ボクセン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水色の髪</t>
+    <rPh sb="0" eb="2">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストライクショット名「マジェスティック・プレアー」</t>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「純然たる炎で燃え尽きよ」というストライクショットボイス</t>
+    <rPh sb="1" eb="3">
+      <t>ジュンゼン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背面の金色の精密な円環の装飾</t>
+    <rPh sb="0" eb="2">
+      <t>ハイメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キンイロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイミツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>エンカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔術の研究や読書を好む</t>
+    <rPh sb="0" eb="2">
+      <t>マジュツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケンキュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ドクショ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金色の鐘</t>
+    <rPh sb="0" eb="2">
+      <t>キンイロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アンチテーゼ」(轟絶・究極)で使われることがあります</t>
+    <rPh sb="9" eb="11">
+      <t>ゴウゼツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キュウキョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背後に浮かぶ青い炎を纏った獣の頭骨</t>
+    <rPh sb="0" eb="2">
+      <t>ハイゴ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケモノ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フード付きの紫色の衣装</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ムラサキイロ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地雷回収と減速壁に対応</t>
+    <rPh sb="0" eb="2">
+      <t>ジライ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゲンソクカベ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界への不和の種を散布</t>
+    <rPh sb="0" eb="2">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>フワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タネ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピード型の戦型</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コウモリのような大きな耳</t>
+    <rPh sb="8" eb="9">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストライクショット名「噂は風に乗り、真を偽り世界を巡り」</t>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウワサ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イツワ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>メグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>点字のようなドットが描かれた白い吹き出し</t>
+    <rPh sb="0" eb="2">
+      <t>テンジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストライクショットボイスの決め台詞「仲違い♪」</t>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゼリフ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ナカタガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収集した情報の風による拡散</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベルトと薔薇による目隠し</t>
+    <rPh sb="4" eb="6">
+      <t>バラ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>メカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界を荒らすもの ポットスターラー</t>
+    <rPh sb="0" eb="2">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1298,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0233801E-AEE7-419F-A025-B14A53D8E071}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="36.58203125" customWidth="1"/>
@@ -1977,6 +2276,226 @@
         <v>62</v>
       </c>
     </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1984,6 +2503,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101003A98CDF2E9D52540902CCB3A4A89A347" ma:contentTypeVersion="5" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="edf6a6dfb2d0c2adb6df272bc5317342">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ff08aa26-24a3-496c-aaff-d3be2242e1de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9d4b6645e0fb865332f6bdb4b29f432" ns3:_="">
     <xsd:import namespace="ff08aa26-24a3-496c-aaff-d3be2242e1de"/>
@@ -2133,15 +2661,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2149,6 +2668,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6104DA49-E359-44CA-A396-FC261DBFC7A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2162,14 +2689,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F7DDDA-8B26-4834-9462-04A1104D76CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
